--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线3层（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="500">
   <si>
     <t>ID</t>
   </si>
@@ -87,6 +87,9 @@
     <t>克拉克的无线电信号最后一次出现是在医院四层的位置，并且持续了大约2分钟才被掐断。尽管存在陷阱的可能，你们也愿意为了这个一同出生入死的同伴赌上一把。</t>
   </si>
   <si>
+    <t>14 enhanced_horror-free</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -268,6 +271,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -921,6 +929,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -962,7 +975,7 @@
     <t>我的意思是，就算真和他有关，背后也肯定有人指使，无论是抓走克拉克的事情，还是别的什么。</t>
   </si>
   <si>
-    <t>jump(70)</t>
+    <t>charfadein(L,1)&amp;jump(70)</t>
   </si>
   <si>
     <t>源类型=type:txt_David; 层级=54; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"视为陷阱","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=70</t>
@@ -1001,7 +1014,7 @@
     <t>行吧，最多5分钟，如果没有找到克拉克的下落，就算你坚持要调查，我也会拎着你的领口把你拖走。</t>
   </si>
   <si>
-    <t>jump(36)</t>
+    <t>charfadein(L,1)&amp;jump(36)</t>
   </si>
   <si>
     <t>源类型=type:txt_David; 层级=29; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"视为陷阱","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=36</t>
@@ -1072,7 +1085,7 @@
     <t>没有，我只知道那家伙给我们的时间并不多，还有不到12分钟。</t>
   </si>
   <si>
-    <t>jump(23)</t>
+    <t>charfadein(L,1)&amp;jump(23)</t>
   </si>
   <si>
     <t>源类型=type:txt_David; 层级=18; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"视为陷阱","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=23</t>
@@ -1173,6 +1186,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -3015,21 +3033,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:12">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -3047,7 +3065,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -3062,12 +3080,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="67.5" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -3085,7 +3103,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -3100,12 +3118,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:12">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -3123,7 +3141,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -3138,12 +3156,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3161,7 +3179,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3176,12 +3194,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3199,7 +3217,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3214,15 +3232,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -3237,7 +3255,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3252,12 +3270,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="67.5" spans="1:12">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3275,7 +3293,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3290,21 +3308,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3313,7 +3331,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3325,15 +3343,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3342,7 +3360,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3351,7 +3369,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3363,15 +3381,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3389,7 +3407,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3404,12 +3422,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3427,7 +3445,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3442,12 +3460,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:12">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3477,15 +3495,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3518,12 +3536,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="67.5" spans="1:12">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3541,7 +3559,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3553,18 +3571,18 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -3579,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3594,12 +3612,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3617,7 +3635,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3632,12 +3650,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3670,21 +3688,21 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="90" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3693,7 +3711,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3705,15 +3723,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="40.5" spans="1:12">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3722,7 +3740,7 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3731,7 +3749,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3743,15 +3761,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3769,7 +3787,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3784,12 +3802,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3807,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3819,15 +3837,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:12">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3845,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3860,12 +3878,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="55.5" spans="1:12">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3883,7 +3901,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3898,12 +3916,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3936,15 +3954,15 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" ht="90" spans="1:12">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -3959,7 +3977,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3974,12 +3992,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" ht="28.5" spans="1:12">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3997,7 +4015,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -4012,12 +4030,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="40.5" spans="1:12">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -4035,7 +4053,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -4050,12 +4068,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -4088,21 +4106,21 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" ht="90" spans="1:12">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4111,7 +4129,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -4123,15 +4141,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" ht="27" spans="1:12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4140,7 +4158,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4149,7 +4167,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4161,15 +4179,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" ht="54" spans="1:12">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4187,7 +4205,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4202,12 +4220,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" ht="55.5" spans="1:12">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4225,7 +4243,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4237,15 +4255,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4278,21 +4296,21 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" ht="90" spans="1:12">
       <c r="A36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4301,7 +4319,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4313,24 +4331,24 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L36" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4339,7 +4357,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4351,15 +4369,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" ht="43.5" spans="1:12">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4377,7 +4395,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4392,12 +4410,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4415,7 +4433,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4427,15 +4445,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4453,7 +4471,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4468,12 +4486,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" ht="28.5" spans="1:12">
       <c r="A41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4491,7 +4509,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4506,12 +4524,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" ht="58.5" spans="1:12">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4529,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4544,12 +4562,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4567,7 +4585,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4582,12 +4600,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" ht="67.5" spans="1:12">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4605,7 +4623,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4617,15 +4635,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" ht="55.5" spans="1:12">
       <c r="A45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4643,7 +4661,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4655,15 +4673,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4681,7 +4699,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4696,12 +4714,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4734,12 +4752,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" ht="90" spans="1:12">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4757,7 +4775,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4769,15 +4787,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4795,7 +4813,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4810,21 +4828,21 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4833,7 +4851,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4845,24 +4863,24 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4871,7 +4889,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4883,12 +4901,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4897,7 +4915,7 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4906,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4918,18 +4936,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4944,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4959,21 +4977,21 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4982,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4994,15 +5012,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -5011,7 +5029,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5020,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -5032,18 +5050,18 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5058,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -5073,21 +5091,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5096,7 +5114,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5108,15 +5126,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5125,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5134,7 +5152,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5146,15 +5164,15 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5187,21 +5205,21 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" ht="90" spans="1:12">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5210,7 +5228,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5222,24 +5240,24 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5248,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5260,24 +5278,24 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5286,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5298,15 +5316,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5315,7 +5333,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5324,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5336,18 +5354,18 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" ht="27" spans="1:12">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -5362,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5377,15 +5395,15 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" ht="28.5" spans="1:12">
       <c r="A65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5400,7 +5418,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5415,12 +5433,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" ht="42" spans="1:12">
       <c r="A66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5438,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5453,12 +5471,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" ht="43.5" spans="1:12">
       <c r="A67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5476,7 +5494,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5488,24 +5506,24 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B68" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5514,7 +5532,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5526,15 +5544,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5543,7 +5561,7 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5552,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5567,21 +5585,21 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70" ht="43.5" spans="1:12">
       <c r="A70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5590,7 +5608,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5605,21 +5623,21 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5628,7 +5646,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5643,21 +5661,21 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" ht="30" spans="1:12">
       <c r="A72" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5666,7 +5684,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5678,15 +5696,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5704,7 +5722,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5719,12 +5737,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5757,12 +5775,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" ht="90" spans="1:12">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5780,7 +5798,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5795,15 +5813,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5818,7 +5836,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5833,12 +5851,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5856,7 +5874,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5871,12 +5889,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5894,7 +5912,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5906,15 +5924,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" ht="42" spans="1:12">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5932,7 +5950,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5947,12 +5965,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5970,7 +5988,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5982,15 +6000,15 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -6008,7 +6026,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -6020,15 +6038,15 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="82" ht="27" spans="1:12">
       <c r="A82" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -6046,7 +6064,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6058,15 +6076,15 @@
         <v>15</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L82" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83" ht="90" spans="1:12">
       <c r="A83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6084,7 +6102,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6096,24 +6114,24 @@
         <v>15</v>
       </c>
       <c r="K83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L83" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" ht="90" spans="1:12">
       <c r="A84" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -6122,7 +6140,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6134,15 +6152,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" ht="90" spans="1:12">
       <c r="A85" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6160,7 +6178,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6171,16 +6189,13 @@
       <c r="J85" t="s">
         <v>15</v>
       </c>
-      <c r="K85" t="s">
-        <v>15</v>
-      </c>
       <c r="L85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6198,7 +6213,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6213,12 +6228,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6236,7 +6251,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6248,24 +6263,24 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="88" ht="90" spans="1:12">
       <c r="A88" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B88" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6274,7 +6289,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6286,18 +6301,18 @@
         <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L88" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" ht="90" spans="1:12">
       <c r="A89" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B89" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -6312,7 +6327,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6324,24 +6339,24 @@
         <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="90" ht="90" spans="1:12">
       <c r="A90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6350,7 +6365,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6362,15 +6377,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L90" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6403,15 +6418,15 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B92" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -6426,7 +6441,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6441,12 +6456,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" ht="27" spans="1:12">
       <c r="A93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6464,7 +6479,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6479,12 +6494,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6517,12 +6532,12 @@
         <v>15</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="95" ht="90" spans="1:12">
       <c r="A95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6540,7 +6555,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6555,12 +6570,12 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="96" ht="27" spans="1:12">
       <c r="A96" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6578,7 +6593,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6593,12 +6608,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="97" ht="27" spans="1:12">
       <c r="A97" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6616,7 +6631,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6631,12 +6646,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6654,7 +6669,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6669,12 +6684,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" ht="54" spans="1:12">
       <c r="A99" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6692,7 +6707,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6704,15 +6719,15 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L99" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" ht="90" spans="1:12">
       <c r="A100" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6730,7 +6745,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6742,10 +6757,10 @@
         <v>15</v>
       </c>
       <c r="K100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L100" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6766,39 +6781,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6806,82 +6821,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -6903,616 +6918,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E18" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E20" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F20" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E21" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F21" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F22" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B24" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D24" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F24" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E25" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F25" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E26" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F26" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B27" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E27" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F27" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B28" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D28" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E28" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F28" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D29" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E30" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F30" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C31" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D31" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线3层（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="501">
   <si>
     <t>ID</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>false</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music14)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=0</t>
@@ -3039,15 +3042,15 @@
         <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -3065,7 +3068,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -3080,12 +3083,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="67.5" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -3103,7 +3106,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -3118,12 +3121,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -3141,7 +3144,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -3156,12 +3159,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3179,7 +3182,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3194,12 +3197,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3217,7 +3220,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3232,15 +3235,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -3255,7 +3258,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3270,12 +3273,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="67.5" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3293,7 +3296,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3308,21 +3311,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3331,7 +3334,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3343,15 +3346,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3360,7 +3363,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3369,7 +3372,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3381,15 +3384,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3407,7 +3410,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3422,12 +3425,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3445,7 +3448,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3460,12 +3463,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:12">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3495,15 +3498,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3536,12 +3539,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="67.5" spans="1:12">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3559,7 +3562,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3571,18 +3574,18 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -3597,7 +3600,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3612,12 +3615,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3635,7 +3638,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3650,12 +3653,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3688,21 +3691,21 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="90" spans="1:12">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
@@ -3711,7 +3714,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3723,15 +3726,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="40.5" spans="1:12">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3740,7 +3743,7 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3749,7 +3752,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3761,15 +3764,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3787,7 +3790,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3802,12 +3805,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3825,7 +3828,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3837,15 +3840,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:12">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3863,7 +3866,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3878,12 +3881,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" ht="55.5" spans="1:12">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3901,7 +3904,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3916,12 +3919,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3954,15 +3957,15 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="90" spans="1:12">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -3977,7 +3980,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3992,12 +3995,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" ht="28.5" spans="1:12">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -4015,7 +4018,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -4030,12 +4033,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="40.5" spans="1:12">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -4053,7 +4056,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -4068,12 +4071,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -4106,21 +4109,21 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" ht="90" spans="1:12">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -4129,7 +4132,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -4141,15 +4144,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4158,7 +4161,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
         <v>15</v>
@@ -4167,7 +4170,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4179,15 +4182,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" ht="54" spans="1:12">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4205,7 +4208,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4220,12 +4223,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" ht="55.5" spans="1:12">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4243,7 +4246,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4255,15 +4258,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4296,21 +4299,21 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" ht="90" spans="1:12">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4319,7 +4322,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4331,24 +4334,24 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4357,7 +4360,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4369,15 +4372,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" ht="43.5" spans="1:12">
       <c r="A38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4395,7 +4398,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4410,12 +4413,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4433,7 +4436,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4445,15 +4448,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4471,7 +4474,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4486,12 +4489,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" ht="28.5" spans="1:12">
       <c r="A41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4509,7 +4512,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4524,12 +4527,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" ht="58.5" spans="1:12">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4547,7 +4550,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4562,12 +4565,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4585,7 +4588,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4600,12 +4603,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" ht="67.5" spans="1:12">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4623,7 +4626,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4635,15 +4638,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" ht="55.5" spans="1:12">
       <c r="A45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4661,7 +4664,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4673,15 +4676,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4699,7 +4702,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4714,12 +4717,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4752,12 +4755,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" ht="90" spans="1:12">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4775,7 +4778,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4787,15 +4790,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L48" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4813,7 +4816,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4828,21 +4831,21 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4851,7 +4854,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4863,24 +4866,24 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
         <v>15</v>
@@ -4889,7 +4892,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4901,12 +4904,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4915,7 +4918,7 @@
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
@@ -4924,7 +4927,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4936,18 +4939,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4962,7 +4965,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4977,21 +4980,21 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -5000,7 +5003,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -5012,15 +5015,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" ht="30" spans="1:12">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -5029,7 +5032,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -5038,7 +5041,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -5050,18 +5053,18 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -5076,7 +5079,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -5091,21 +5094,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -5114,7 +5117,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5126,15 +5129,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" ht="30" spans="1:12">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5143,7 +5146,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5152,7 +5155,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5164,15 +5167,15 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5205,21 +5208,21 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" ht="90" spans="1:12">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
@@ -5228,7 +5231,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5240,24 +5243,24 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
@@ -5266,7 +5269,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5278,24 +5281,24 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
@@ -5304,7 +5307,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5316,15 +5319,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L62" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5333,7 +5336,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5342,7 +5345,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5354,18 +5357,18 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" ht="27" spans="1:12">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -5380,7 +5383,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5395,15 +5398,15 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" ht="28.5" spans="1:12">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5418,7 +5421,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5433,12 +5436,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" ht="42" spans="1:12">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5456,7 +5459,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5471,12 +5474,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" ht="43.5" spans="1:12">
       <c r="A67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5494,7 +5497,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5506,24 +5509,24 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L67" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5532,7 +5535,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5544,15 +5547,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5561,7 +5564,7 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5570,7 +5573,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5585,21 +5588,21 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" ht="43.5" spans="1:12">
       <c r="A70" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5608,7 +5611,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5623,21 +5626,21 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5646,7 +5649,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5661,21 +5664,21 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" ht="30" spans="1:12">
       <c r="A72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5684,7 +5687,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5696,15 +5699,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L72" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5722,7 +5725,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5737,12 +5740,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5775,12 +5778,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" ht="90" spans="1:12">
       <c r="A75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5798,7 +5801,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5813,15 +5816,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5836,7 +5839,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5851,12 +5854,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5874,7 +5877,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5889,12 +5892,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5912,7 +5915,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5924,15 +5927,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79" ht="42" spans="1:12">
       <c r="A79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5950,7 +5953,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5965,12 +5968,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5988,7 +5991,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -6000,15 +6003,15 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -6026,7 +6029,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -6038,15 +6041,15 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L81" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" ht="27" spans="1:12">
       <c r="A82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -6064,7 +6067,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6076,15 +6079,15 @@
         <v>15</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L82" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" ht="90" spans="1:12">
       <c r="A83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6102,7 +6105,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6114,24 +6117,24 @@
         <v>15</v>
       </c>
       <c r="K83" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L83" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" ht="90" spans="1:12">
       <c r="A84" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -6140,7 +6143,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6152,15 +6155,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L84" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" ht="90" spans="1:12">
       <c r="A85" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6178,7 +6181,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6190,12 +6193,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6213,7 +6216,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6228,12 +6231,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6251,7 +6254,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6263,24 +6266,24 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88" ht="90" spans="1:12">
       <c r="A88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6289,7 +6292,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6301,18 +6304,18 @@
         <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="89" ht="90" spans="1:12">
       <c r="A89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -6327,7 +6330,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6339,24 +6342,24 @@
         <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="90" ht="90" spans="1:12">
       <c r="A90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B90" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6365,7 +6368,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6377,15 +6380,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L90" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6418,15 +6421,15 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -6441,7 +6444,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6456,12 +6459,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="93" ht="27" spans="1:12">
       <c r="A93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6479,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6494,12 +6497,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6532,12 +6535,12 @@
         <v>15</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="95" ht="90" spans="1:12">
       <c r="A95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6555,7 +6558,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6570,12 +6573,12 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" ht="27" spans="1:12">
       <c r="A96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6593,7 +6596,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6608,12 +6611,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97" ht="27" spans="1:12">
       <c r="A97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6631,7 +6634,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6646,12 +6649,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6669,7 +6672,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6684,12 +6687,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="99" ht="54" spans="1:12">
       <c r="A99" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6707,7 +6710,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6719,15 +6722,15 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L99" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="100" ht="90" spans="1:12">
       <c r="A100" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6745,7 +6748,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6757,10 +6760,10 @@
         <v>15</v>
       </c>
       <c r="K100" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L100" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -6781,39 +6784,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6821,82 +6824,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -6918,616 +6921,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D13" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D15" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E15" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D18" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E18" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F18" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D20" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E20" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F20" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D21" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E21" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F21" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E22" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F22" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D24" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E24" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D25" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E25" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D26" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E26" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F26" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D27" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E27" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F27" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C28" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D28" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E28" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F28" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C29" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D30" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E30" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F30" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B31" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C31" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
